--- a/out/Attention-MambaAMT_repeat_3_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.668078547550069</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.668078547550069</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.268078547550068</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.268078547550068</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.268078547550068</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.268078547550068</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4348469049778109</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4348469049778109</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.268078547550068</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.668078547550069</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.668078547550069</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.668078547550069</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.668078547550069</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.668078547550069</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.668078547550069</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.668078547550069</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.668078547550069</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.668078547550069</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.668078547550069</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.668078547550069</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.668078547550069</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.668078547550069</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.295895168639794</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.668078547550069</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.295895168639794</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.668078547550069</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.295895168639794</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.668078547550069</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.668078547550069</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.268078547550068</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.268078547550068</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.268078547550068</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.268078547550068</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.668078547550069</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.668078547550069</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.268078547550068</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.268078547550068</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.268078547550068</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.268078547550068</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4348469049778109</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4348469049778109</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002852461982754757</v>
+        <v>-6.448379311920143e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1228186240889292</v>
+        <v>0.02776484910029164</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.268078547550068</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2459652335842342</v>
+        <v>0.05560379524204508</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.474514125262715</v>
+        <v>0.107269468228107</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.668078547550069</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.072488725084198</v>
+        <v>0.2424505407967612</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1459632049202166</v>
+        <v>0.03299719876048084</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.8893003148215329</v>
+        <v>0.2010380191454471</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02961681348275625</v>
+        <v>0.006694603805886263</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8023428051754744</v>
+        <v>0.1813793875539452</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02564983452094541</v>
+        <v>0.005796268188900115</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.8239925053630751</v>
+        <v>0.1862717017465942</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01253927213630021</v>
+        <v>0.002831471832630831</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8233888297036842</v>
+        <v>0.1861316771016896</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00598248580713162</v>
+        <v>0.001348715684103188</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8227998176996869</v>
+        <v>0.1859946445470252</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002489618419825244</v>
+        <v>0.0005589474356801993</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.821789025640114</v>
+        <v>0.185762269551188</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001723544137658513</v>
+        <v>0.0003854657739532177</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8227450091788431</v>
+        <v>0.1859745154714098</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007166014665040973</v>
+        <v>0.0001580046169870863</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8224526613928564</v>
+        <v>0.185904506931341</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003691761022200321</v>
+        <v>7.985779461061441e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8224736840023049</v>
+        <v>0.1859054030642214</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001419619442060651</v>
+        <v>2.806643744636465e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8223878480090054</v>
+        <v>0.1858821037689613</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.516865658702444e-05</v>
+        <v>1.332426436274844e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8223961072986871</v>
+        <v>0.185880123531959</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.452702125317959e-05</v>
+        <v>4.034747715012475e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8223898940561505</v>
+        <v>0.1858748480413437</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.364889654592446e-05</v>
+        <v>-7.373950752172664e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8223825869453585</v>
+        <v>0.1858693279895917</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.301093358848441e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8223749835814947</v>
+        <v>0.1858637494642888</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8223691128551907</v>
+        <v>0.1858585559695547</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8223632480591894</v>
+        <v>0.1858533636838377</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8223575688824812</v>
+        <v>0.1858532281752319</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8223526875842319</v>
+        <v>0.1858532680307042</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.822347766382684</v>
+        <v>0.1858533078861765</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8223477584115896</v>
+        <v>0.1858532999150821</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8223479178334786</v>
+        <v>0.1858534593369712</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.1858533636838377</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8223481729085015</v>
+        <v>0.185853714411994</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8223479258045732</v>
+        <v>0.1858534673080656</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8223478859491008</v>
+        <v>0.1858534274525933</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.1858533636838377</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8223478939201952</v>
+        <v>0.1858534354236878</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>2.268078547550068</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.1858533636838377</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.268078547550068</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8223479258045732</v>
+        <v>0.1858534673080656</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8223480214577068</v>
+        <v>0.1858535629611993</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.822347957688951</v>
+        <v>0.1858534991924435</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8223479178334786</v>
+        <v>0.1858534593369712</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8223478939201952</v>
+        <v>0.1858534354236878</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8223476468162672</v>
+        <v>0.1858531883197597</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8223475671053224</v>
+        <v>0.1858531086088149</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8223476149318891</v>
+        <v>0.1858531564353816</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8223477344983062</v>
+        <v>0.1858532760017987</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8223477185561172</v>
+        <v>0.1858532600596098</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8223477344983062</v>
+        <v>0.1858532760017987</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8223477185561172</v>
+        <v>0.1858532600596098</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8223477743537785</v>
+        <v>0.185853315857271</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8223477743537785</v>
+        <v>0.185853315857271</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8223477743537785</v>
+        <v>0.185853315857271</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8223479258045732</v>
+        <v>0.1858534673080656</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8223481410241237</v>
+        <v>0.1858536825276162</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8223480533420846</v>
+        <v>0.1858535948455771</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8223480055155179</v>
+        <v>0.1858535470190104</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8223480533420846</v>
+        <v>0.1858535948455771</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8223478700069119</v>
+        <v>0.1858534115104044</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8223478779780063</v>
+        <v>0.1858534194814989</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8223478859491008</v>
+        <v>0.1858534274525933</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8223478939201952</v>
+        <v>0.1858534354236878</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8223478939201952</v>
+        <v>0.1858534354236878</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8223479337756676</v>
+        <v>0.1858534752791601</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8223479975444234</v>
+        <v>0.185853539047916</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8223481091397459</v>
+        <v>0.1858536506432383</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8223481569663126</v>
+        <v>0.1858536984698051</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8223481171108403</v>
+        <v>0.1858536586143328</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8223480453709902</v>
+        <v>0.1858535868744827</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.822348164937407</v>
+        <v>0.1858537064408995</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8223480055155179</v>
+        <v>0.1858535470190104</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8223477743537785</v>
+        <v>0.185853315857271</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8223477265272118</v>
+        <v>0.1858532680307042</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8223477584115896</v>
+        <v>0.1858532999150821</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.1858533636838377</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.1858533636838377</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8223477424694007</v>
+        <v>0.1858532839728931</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8223476229029836</v>
+        <v>0.1858531644064761</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8223475830475113</v>
+        <v>0.1858531245510038</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8223477265272118</v>
+        <v>0.1858532680307042</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8223478620358174</v>
+        <v>0.18585340353931</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8223478460936285</v>
+        <v>0.1858533875971211</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.1858533636838377</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8223477823248729</v>
+        <v>0.1858533238283654</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.295895168639794</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.822347678700645</v>
+        <v>0.1858532202041375</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.295895168639794</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.822347559134228</v>
+        <v>0.1858531006377204</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4348469049778109</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.822347678700645</v>
+        <v>0.1858532202041375</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4348469049778109</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8223477265272118</v>
+        <v>0.1858532680307042</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.1858533636838377</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.295895168639794</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8223477026139283</v>
+        <v>0.1858532441174209</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.295895168639794</v>
+        <v>2.967222099549091</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8223477105850228</v>
+        <v>0.1858532520885153</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_3_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.295895168639794</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.295895168639794</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.295895168639794</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.668078547550069</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052214</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.295895168639794</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002852461982754757</v>
+        <v>-0.0002232922492276411</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1228186240889292</v>
+        <v>0.09614315946984622</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2459652335842342</v>
+        <v>0.1925428996128948</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.474514125262715</v>
+        <v>0.3714510432781228</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052214</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.072488725084198</v>
+        <v>0.8395493457442964</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1459632049202166</v>
+        <v>0.114260932171624</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.8893003148215329</v>
+        <v>0.6961482842843821</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02961681348275625</v>
+        <v>0.02318439308455688</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8023428051754744</v>
+        <v>0.6280773879577692</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02564983452094541</v>
+        <v>0.02007835700441365</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.8239925053630751</v>
+        <v>0.6450247947110506</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01253927213630021</v>
+        <v>0.009816202883176649</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8233888297036842</v>
+        <v>0.6445522277077951</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00598248580713162</v>
+        <v>0.004682223851917009</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8227998176996869</v>
+        <v>0.6440900666164963</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002489618419825244</v>
+        <v>0.001947382682063631</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.821789025640114</v>
+        <v>0.6432977841323272</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001723544137658513</v>
+        <v>0.001348511793505818</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8227450091788431</v>
+        <v>0.6440451000393983</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007166014665040973</v>
+        <v>0.0005600397197536547</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8224526613928564</v>
+        <v>0.6438151963269761</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003691761022200321</v>
+        <v>0.0002876591656649537</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8224736840023049</v>
+        <v>0.64383055493476</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001419619442060651</v>
+        <v>0.0001099452349326009</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8223878480090054</v>
+        <v>0.6437622983819234</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.516865658702444e-05</v>
+        <v>5.798965874694777e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8223961072986871</v>
+        <v>0.6437676788172282</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.452702125317959e-05</v>
+        <v>2.605694527035538e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8223898940561505</v>
+        <v>0.6437617318182378</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.364889654592446e-05</v>
+        <v>9.386291621141726e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8223825869453585</v>
+        <v>0.6437549447591978</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.301093358848441e-06</v>
+        <v>1.456405945771008e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8223749835814947</v>
+        <v>0.6437479199206371</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-2.106181251314092e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8223691128551907</v>
+        <v>0.6437422426890672</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8223632480591894</v>
+        <v>0.6437365701787831</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8223575688824812</v>
+        <v>0.6437310265106806</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8223526875842319</v>
+        <v>0.6437261053569592</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.822347766382684</v>
+        <v>0.6437261452124314</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8223477584115896</v>
+        <v>0.643726137241337</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8223479178334786</v>
+        <v>0.6437262966632261</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.6437262010100926</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8223481729085015</v>
+        <v>0.6437265517382489</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8223479258045732</v>
+        <v>0.6437263046343206</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8223478859491008</v>
+        <v>0.6437262647788483</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.6437262010100926</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.295895168639794</v>
+        <v>0.1545801623475385</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8223478939201952</v>
+        <v>0.6437262727499428</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.6437262010100926</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052214</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8223479258045732</v>
+        <v>0.6437263046343206</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6958951686397941</v>
+        <v>0.1545801623475385</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8223480214577068</v>
+        <v>0.6437264002874542</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.5228995442101445</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.822347957688951</v>
+        <v>0.6437263365186984</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8223479178334786</v>
+        <v>0.6437262966632261</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8223478939201952</v>
+        <v>0.6437262727499428</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8223476468162672</v>
+        <v>0.6437260256460146</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8223475671053224</v>
+        <v>0.6437259459350698</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8223476149318891</v>
+        <v>0.6437259937616365</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8223477344983062</v>
+        <v>0.6437261133280536</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8223477185561172</v>
+        <v>0.6437260973858647</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8223477344983062</v>
+        <v>0.6437261133280536</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8223477185561172</v>
+        <v>0.6437260973858647</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8223477743537785</v>
+        <v>0.6437261531835259</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8223477743537785</v>
+        <v>0.6437261531835259</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8223477743537785</v>
+        <v>0.6437261531835259</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8223479258045732</v>
+        <v>0.6437263046343206</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8223481410241237</v>
+        <v>0.6437265198538711</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8223480533420846</v>
+        <v>0.6437264321718321</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8223480055155179</v>
+        <v>0.6437263843452653</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8223480533420846</v>
+        <v>0.6437264321718321</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8223478700069119</v>
+        <v>0.6437262488366594</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8223478779780063</v>
+        <v>0.6437262568077539</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8223478859491008</v>
+        <v>0.6437262647788483</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8223478939201952</v>
+        <v>0.6437262727499428</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8223478939201952</v>
+        <v>0.6437262727499428</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8223479337756676</v>
+        <v>0.643726312605415</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8223479975444234</v>
+        <v>0.6437263763741708</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8223481091397459</v>
+        <v>0.6437264879694933</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8223481569663126</v>
+        <v>0.64372653579606</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8223481171108403</v>
+        <v>0.6437264959405877</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8223480453709902</v>
+        <v>0.6437264242007377</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.822348164937407</v>
+        <v>0.6437265437671544</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8223480055155179</v>
+        <v>0.6437263843452653</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8223477743537785</v>
+        <v>0.6437261531835259</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8223477265272118</v>
+        <v>0.6437261053569592</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8223477584115896</v>
+        <v>0.643726137241337</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.6437262010100926</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.6437262010100926</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8223477424694007</v>
+        <v>0.6437261212991481</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8223476229029836</v>
+        <v>0.643726001732731</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8223475830475113</v>
+        <v>0.6437259618772587</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8223477265272118</v>
+        <v>0.6437261053569592</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8223478620358174</v>
+        <v>0.643726240865565</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8223478460936285</v>
+        <v>0.6437262249233759</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.6437262010100926</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8223477823248729</v>
+        <v>0.6437261611546203</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.822347678700645</v>
+        <v>0.6437260575303925</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.822347559134228</v>
+        <v>0.6437259379639754</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.822347678700645</v>
+        <v>0.6437260575303925</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8223477265272118</v>
+        <v>0.6437261053569592</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8223478221803452</v>
+        <v>0.6437262010100926</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8223477026139283</v>
+        <v>0.6437260814436758</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8223477105850228</v>
+        <v>0.6437260894147703</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_3_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01072476431727409</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.02064332738518715</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.09000000000000005</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01529337838292122</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.509539575462904</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.009067609906196594</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.509539575462904</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.001910749822854996</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.509539575462904</v>
+        <v>0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.004377976059913635</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.509539575462904</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.00905899703502655</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.509539575462904</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0089564248919487</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.509539575462904</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.01244310289621353</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.509539575462904</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.01543515920639038</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.309539575462904</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.009559910744428635</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.309539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.01160553097724915</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.309539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01885664090514183</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.309539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.01900060847401619</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.309539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.02479769662022591</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.309539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.01492561772465706</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.309539575462904</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01413075253367424</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.00757540762424469</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01762450858950615</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01690136641263962</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01287422701716423</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.004533495754003525</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.6320598689052213</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.003495350480079651</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.6320598689052213</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002167344093322754</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04541983765246159</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.0004925951361656189</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6320598689052213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.009211353957653046</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04541983765246159</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0005175098776817322</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6320598689052213</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.011843241751194</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6320598689052213</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001628514379262924</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.509539575462904</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.005401059985160828</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.509539575462904</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.009869854897260666</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.509539575462904</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.0005794763565063477</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.509539575462904</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.007184520363807678</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.8320598689052214</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.00134991854429245</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.8320598689052213</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.009114816784858704</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.6320598689052213</v>
+        <v>0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0108470730483532</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.309539575462904</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01053587347269058</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.509539575462904</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.01616997271776199</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.509539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.04120904207229614</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.509539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.03680762648582458</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.509539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.02518933452665806</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.509539575462904</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01879003271460533</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.509539575462904</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002232922492276411</v>
+        <v>-0.0001473718101831619</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09614315946984622</v>
+        <v>0.06345391560930431</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01115619018673897</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.509539575462904</v>
+        <v>-0.3</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1925428996128948</v>
+        <v>0.1270773879135698</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3714510432781228</v>
+        <v>0.2451568611862512</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.00136842206120491</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.6320598689052214</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8395493457442964</v>
+        <v>0.5540992489817671</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.114260932171624</v>
+        <v>0.07541111576779003</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.01175772398710251</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04541983765246159</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.6961482842843821</v>
+        <v>0.4594552905944062</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02318439308455688</v>
+        <v>0.01530147634608275</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0129489004611969</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6280773879577692</v>
+        <v>0.4145285482217036</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02007835700441365</v>
+        <v>0.01325175855749444</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.02194011956453323</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6450247947110506</v>
+        <v>0.4257139759042717</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009816202883176649</v>
+        <v>0.006477164158480131</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.005327347666025162</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6445522277077951</v>
+        <v>0.4254004052695686</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004682223851917009</v>
+        <v>0.003088634559426337</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.02011448889970779</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6440900666164963</v>
+        <v>0.4250936724324035</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001947382682063631</v>
+        <v>0.001283784120039152</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01584764569997787</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6432977841323272</v>
+        <v>0.4245690543520839</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001348511793505818</v>
+        <v>0.0008878239139602231</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01182561367750168</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6440451000393983</v>
+        <v>0.4250605235650672</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005600397197536547</v>
+        <v>0.0003680421867016718</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0005210861563682556</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6438151963269761</v>
+        <v>0.4249070409544716</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002876591656649537</v>
+        <v>0.0001881015956099809</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.009434446692466736</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.64383055493476</v>
+        <v>0.4249154820520258</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001099452349326009</v>
+        <v>7.110529253528369e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.02765415608882904</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6437622983819234</v>
+        <v>0.4248686948574835</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.798965874694777e-05</v>
+        <v>3.622959481618401e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01752138882875443</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6437676788172282</v>
+        <v>0.4248705371507951</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.605694527035538e-05</v>
+        <v>1.532818235877807e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01421041041612625</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6437617318182378</v>
+        <v>0.4248649093258159</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.386291621141726e-06</v>
+        <v>4.59086108076115e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.01197920739650726</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6437549447591978</v>
+        <v>0.4248587073249966</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>-8.494533205757797e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.009225957095623016</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6437479199206371</v>
+        <v>0.4248523339032144</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01708605140447617</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6437422426890672</v>
+        <v>0.4248468501663788</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.04640701416283e-06</v>
+        <v>-4.36427134277522e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.01849174499511719</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6437365701787831</v>
+        <v>0.4248413699418115</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.006866905838251114</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6437310265106806</v>
+        <v>0.4248359625991546</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01326296478509903</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6437261053569592</v>
+        <v>0.4248310414454332</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.001709796488285065</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6437261452124314</v>
+        <v>0.4248310813009055</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.004618428647518158</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.643726137241337</v>
+        <v>0.424831073329811</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.005047030746936798</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6437262966632261</v>
+        <v>0.4248312327517001</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.002317316830158234</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6437262010100926</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.02244798094034195</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6437265517382489</v>
+        <v>0.4248314878267229</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.01524151861667633</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6437263046343206</v>
+        <v>0.4248312407227945</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.02348373830318451</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6437262647788483</v>
+        <v>0.4248312008673223</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.0160285010933876</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6437262010100926</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01707398146390915</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.1545801623475385</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6437262727499428</v>
+        <v>0.4248312088384167</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.008213367313146591</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8320598689052213</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6437262010100926</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.002971291542053223</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.8320598689052214</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6437263046343206</v>
+        <v>0.4248312407227945</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.02538331598043442</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.1545801623475385</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6437264002874542</v>
+        <v>0.4248313363759282</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.02866237610578537</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5228995442101445</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6437263365186984</v>
+        <v>0.4248312726071723</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.00862797349691391</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6437262966632261</v>
+        <v>0.4248312327517001</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01782183349132538</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6437262727499428</v>
+        <v>0.4248312088384167</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.02523046731948853</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6437260256460146</v>
+        <v>0.4248309617344886</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.009454883635044098</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6437259459350698</v>
+        <v>0.4248308820235438</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.003657851368188858</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6437259937616365</v>
+        <v>0.4248309298501106</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.009549438953399658</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6437261133280536</v>
+        <v>0.4248310494165276</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.01347092539072037</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6437260973858647</v>
+        <v>0.4248310334743387</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.008458055555820465</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6437261133280536</v>
+        <v>0.4248310494165276</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.01009482890367508</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6437260973858647</v>
+        <v>0.4248310334743387</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.01689719408750534</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6437261531835259</v>
+        <v>0.4248310892719999</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-2.957507967948914e-05</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6437261531835259</v>
+        <v>0.4248310892719999</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.005132511258125305</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6437261531835259</v>
+        <v>0.4248310892719999</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.004089575260877609</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6437263046343206</v>
+        <v>0.4248312407227945</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.007949717342853546</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6437265198538711</v>
+        <v>0.4248314559423451</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.02004531770944595</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6437264321718321</v>
+        <v>0.4248313682603061</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.005401294678449631</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6437263843452653</v>
+        <v>0.4248313204337393</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.02121526747941971</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6437264321718321</v>
+        <v>0.4248313682603061</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.01580310612916946</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6437262488366594</v>
+        <v>0.4248311849251334</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.009895876049995422</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6437262568077539</v>
+        <v>0.4248311928962278</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01320683211088181</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6437262647788483</v>
+        <v>0.4248312008673223</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.008411385118961334</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.16</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6437262727499428</v>
+        <v>0.4248312088384167</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.001159213483333588</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6437262727499428</v>
+        <v>0.4248312088384167</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.008469030261039734</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.643726312605415</v>
+        <v>0.424831248693889</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.01178865879774094</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6437263763741708</v>
+        <v>0.4248313124626449</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01728815585374832</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.16</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6437264879694933</v>
+        <v>0.4248314240579673</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.01057485491037369</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.64372653579606</v>
+        <v>0.424831471884534</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.005386888980865479</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6437264959405877</v>
+        <v>0.4248314320290617</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.009736113250255585</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6437264242007377</v>
+        <v>0.4248313602892116</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01556626707315445</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6437265437671544</v>
+        <v>0.4248314798556285</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.02015452831983566</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6437263843452653</v>
+        <v>0.4248313204337393</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.02494336664676666</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6437261531835259</v>
+        <v>0.4248310892719999</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.009580269455909729</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6437261053569592</v>
+        <v>0.4248310414454332</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.003972560167312622</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.643726137241337</v>
+        <v>0.424831073329811</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01500912755727768</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.16</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6437262010100926</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01101795583963394</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6437262010100926</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01373345404863358</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.16</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6437261212991481</v>
+        <v>0.4248310573876221</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.01140563935041428</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.3</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.643726001732731</v>
+        <v>0.424830937821205</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.000938069075345993</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6437259618772587</v>
+        <v>0.4248308979657328</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.01101230084896088</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6437261053569592</v>
+        <v>0.4248310414454332</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.00890514999628067</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.643726240865565</v>
+        <v>0.4248311769540389</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.00931500643491745</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6437262249233759</v>
+        <v>0.42483116101185</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.01137133687734604</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6437262010100926</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.009189791977405548</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6437261611546203</v>
+        <v>0.4248310972430944</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.0132138654589653</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6437260575303925</v>
+        <v>0.4248309936188664</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.007563754916191101</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6437259379639754</v>
+        <v>0.4248308740524493</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.009901218116283417</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6437260575303925</v>
+        <v>0.4248309936188664</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01236841827630997</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6437261053569592</v>
+        <v>0.4248310414454332</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.01179928332567215</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6437262010100926</v>
+        <v>0.4248311370985666</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.008769862353801727</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6437260814436758</v>
+        <v>0.4248310175321498</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.01837379485368729</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6437260894147703</v>
+        <v>0.4248310255032443</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_3_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000001.xlsx
@@ -50234,7 +50234,7 @@
         <v>-0.006866905838251114</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC62" t="n">
         <v>0.4248359625991546</v>
@@ -51029,7 +51029,7 @@
         <v>-0.01326296478509903</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0.4248310414454332</v>
@@ -51824,7 +51824,7 @@
         <v>-0.001709796488285065</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0.4248310813009055</v>
@@ -52619,7 +52619,7 @@
         <v>-0.004618428647518158</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC65" t="n">
         <v>0.424831073329811</v>
@@ -53414,7 +53414,7 @@
         <v>-0.005047030746936798</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC66" t="n">
         <v>0.4248312327517001</v>
@@ -55799,7 +55799,7 @@
         <v>-0.01524151861667633</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0.4248312407227945</v>
